--- a/data/samples/samples/PL-6-2-A12H_D03_2026-03-03.xlsx
+++ b/data/samples/samples/PL-6-2-A12H_D03_2026-03-03.xlsx
@@ -1076,7 +1076,7 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>06:00 06:30 钻进至 2353.58 m，钻压 126 kN，转速 158 rpm，排量 32 L/s，钻时 18.9 m/h。</t>
+          <t>06:30 06:30 钻进至 2353.58 m，钻压 126 kN，转速 158 rpm，排量 32 L/s，钻时 18.9 m/h。</t>
         </is>
       </c>
     </row>
@@ -1104,21 +1104,21 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>16:00 16:30 短起下检查井眼，返砂正常。</t>
+          <t>16:30 16:30 短起下检查井眼，返砂正常。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>18:00 18:15 地质录井汇报：岩性为灰色细砂岩，荧光显示 3 级。</t>
+          <t>18:15 18:15 地质录井汇报：岩性为灰色细砂岩，荧光显示 3 级。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>20:00 20:45 地质录井汇报：岩性为灰色细砂岩，荧光显示 3 级。</t>
+          <t>20:45 20:45 地质录井汇报：岩性为灰色细砂岩，荧光显示 3 级。</t>
         </is>
       </c>
     </row>
